--- a/data/trans_orig/P23_1_2016_2023_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66002</t>
+          <t>65354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97611</t>
+          <t>97278</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70671</t>
+          <t>68685</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115162</t>
+          <t>113570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156367</t>
+          <t>156029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196150</t>
+          <t>196483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>227759</t>
+          <t>228407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218032</t>
+          <t>220018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246133</t>
+          <t>246268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426097</t>
+          <t>426435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>467302</t>
+          <t>468894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68971</t>
+          <t>69477</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103430</t>
+          <t>103827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52927</t>
+          <t>51770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104409</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>144932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398281</t>
+          <t>397884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>432740</t>
+          <t>432234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467959</t>
+          <t>469116</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493479</t>
+          <t>492758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877120</t>
+          <t>877665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>918188</t>
+          <t>920504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>56504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84072</t>
+          <t>84395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41177</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83215</t>
+          <t>83321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119849</t>
+          <t>119078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234493</t>
+          <t>234170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262118</t>
+          <t>262061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295132</t>
+          <t>295360</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315180</t>
+          <t>315733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535025</t>
+          <t>535796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>571659</t>
+          <t>571553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83028</t>
+          <t>83422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117735</t>
+          <t>115904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38474</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66035</t>
+          <t>64607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128185</t>
+          <t>127849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173507</t>
+          <t>173683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>252229</t>
+          <t>254060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>286936</t>
+          <t>286542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319963</t>
+          <t>321391</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347524</t>
+          <t>347131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>582455</t>
+          <t>582279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>627777</t>
+          <t>628113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>57805</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54344</t>
+          <t>52100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83790</t>
+          <t>83171</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154465</t>
+          <t>153416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177437</t>
+          <t>176506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186339</t>
+          <t>187195</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204077</t>
+          <t>204546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346018</t>
+          <t>346637</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375464</t>
+          <t>377708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39793</t>
+          <t>39964</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65066</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53596</t>
+          <t>54619</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83075</t>
+          <t>84129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>198057</t>
+          <t>197961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223330</t>
+          <t>223159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247602</t>
+          <t>246835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262806</t>
+          <t>262711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>453163</t>
+          <t>452109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482642</t>
+          <t>481619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110112</t>
+          <t>111469</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157642</t>
+          <t>152842</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71166</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108745</t>
+          <t>105026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>189813</t>
+          <t>193381</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>245991</t>
+          <t>248705</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>497844</t>
+          <t>502644</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>545374</t>
+          <t>544017</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>580594</t>
+          <t>584313</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>618173</t>
+          <t>619621</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1098834</t>
+          <t>1096120</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1155012</t>
+          <t>1151444</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>121065</t>
+          <t>119377</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>165344</t>
+          <t>168070</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68268</t>
+          <t>71270</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>109203</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>199512</t>
+          <t>200174</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>257675</t>
+          <t>257220</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>613239</t>
+          <t>610513</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>657518</t>
+          <t>659206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>719199</t>
+          <t>716964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>757899</t>
+          <t>754897</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1347075</t>
+          <t>1347530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1405238</t>
+          <t>1404576</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>657162</t>
+          <t>657993</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>752570</t>
+          <t>752729</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>351550</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>424406</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1034000</t>
+          <t>1025856</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1154938</t>
+          <t>1154919</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2639844</t>
+          <t>2639685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2735252</t>
+          <t>2734421</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3114697</t>
+          <t>3111801</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3187471</t>
+          <t>3187553</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5776579</t>
+          <t>5776598</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5897517</t>
+          <t>5905661</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36379</t>
+          <t>35596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61392</t>
+          <t>60566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46821</t>
+          <t>47470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72782</t>
+          <t>73603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250051</t>
+          <t>250877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275064</t>
+          <t>275847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272160</t>
+          <t>271413</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281955</t>
+          <t>281730</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>528295</t>
+          <t>527474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554256</t>
+          <t>553607</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92632</t>
+          <t>91072</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134079</t>
+          <t>135099</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>52539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80239</t>
+          <t>79017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153549</t>
+          <t>154456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202542</t>
+          <t>206532</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384311</t>
+          <t>383291</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>425758</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>434730</t>
+          <t>435952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462520</t>
+          <t>462430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>830817</t>
+          <t>826827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>879810</t>
+          <t>878903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>54830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81833</t>
+          <t>82179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39350</t>
+          <t>39791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62240</t>
+          <t>62009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101384</t>
+          <t>101875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136717</t>
+          <t>136768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234217</t>
+          <t>233871</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>259659</t>
+          <t>261220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>286888</t>
+          <t>287119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309778</t>
+          <t>309337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>528461</t>
+          <t>528410</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>563794</t>
+          <t>563303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78880</t>
+          <t>78211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113968</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34063</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76438</t>
+          <t>77721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113917</t>
+          <t>111080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182768</t>
+          <t>182201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198589</t>
+          <t>197499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233677</t>
+          <t>234346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>399280</t>
+          <t>397997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441655</t>
+          <t>440788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>605506</t>
+          <t>606073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>674357</t>
+          <t>677194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30266</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157643</t>
+          <t>157868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168590</t>
+          <t>169058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195946</t>
+          <t>195288</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203387</t>
+          <t>203486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357132</t>
+          <t>357095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>370479</t>
+          <t>370580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55555</t>
+          <t>56427</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45306</t>
+          <t>46876</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68477</t>
+          <t>70213</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214081</t>
+          <t>213209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234086</t>
+          <t>233395</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240109</t>
+          <t>239934</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249943</t>
+          <t>250071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>458215</t>
+          <t>456479</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481386</t>
+          <t>479816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103463</t>
+          <t>104130</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144004</t>
+          <t>141819</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>39596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134783</t>
+          <t>131943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135531</t>
+          <t>138258</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262893</t>
+          <t>262808</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>479081</t>
+          <t>481266</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>519622</t>
+          <t>518955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710576</t>
+          <t>713416</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>801363</t>
+          <t>805763</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1205551</t>
+          <t>1205636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1332913</t>
+          <t>1330186</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132489</t>
+          <t>130443</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>669981</t>
+          <t>654262</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48580</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158695</t>
+          <t>158441</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>872938</t>
+          <t>853817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>257736</t>
+          <t>273455</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>795228</t>
+          <t>797274</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>669151</t>
+          <t>669311</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>688960</t>
+          <t>688626</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>772511</t>
+          <t>791632</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1486754</t>
+          <t>1487008</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>637003</t>
+          <t>641386</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1404653</t>
+          <t>1477012</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>261388</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>376266</t>
+          <t>377059</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>946969</t>
+          <t>950224</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1975074</t>
+          <t>1829952</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2052967</t>
+          <t>1980608</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2820617</t>
+          <t>2816234</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3281985</t>
+          <t>3281192</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3396863</t>
+          <t>3382553</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5140797</t>
+          <t>5285919</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6168902</t>
+          <t>6165647</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65354</t>
+          <t>64783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97278</t>
+          <t>95566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68685</t>
+          <t>69961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113570</t>
+          <t>116162</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156029</t>
+          <t>157379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196483</t>
+          <t>198195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228407</t>
+          <t>228978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220018</t>
+          <t>218742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246268</t>
+          <t>246667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426435</t>
+          <t>425085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>468894</t>
+          <t>466302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69477</t>
+          <t>69234</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103827</t>
+          <t>105840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>52277</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102093</t>
+          <t>104339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144932</t>
+          <t>148101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397884</t>
+          <t>395871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>432234</t>
+          <t>432477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469116</t>
+          <t>468609</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492758</t>
+          <t>492697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877665</t>
+          <t>874496</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920504</t>
+          <t>918258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84395</t>
+          <t>87100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40949</t>
+          <t>40137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83321</t>
+          <t>84482</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119078</t>
+          <t>118636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234170</t>
+          <t>231465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262061</t>
+          <t>262118</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295360</t>
+          <t>296172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315733</t>
+          <t>315702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535796</t>
+          <t>536238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>571553</t>
+          <t>570392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83422</t>
+          <t>82153</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115904</t>
+          <t>117643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>38960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64607</t>
+          <t>65592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127849</t>
+          <t>127585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173683</t>
+          <t>170913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254060</t>
+          <t>252321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>286542</t>
+          <t>287811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>321391</t>
+          <t>320406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347131</t>
+          <t>347038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>582279</t>
+          <t>585049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>628113</t>
+          <t>628377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34715</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57805</t>
+          <t>56033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52100</t>
+          <t>52292</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83171</t>
+          <t>81879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153416</t>
+          <t>155188</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176506</t>
+          <t>177500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187195</t>
+          <t>186525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204546</t>
+          <t>204286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346637</t>
+          <t>347929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377708</t>
+          <t>377516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39964</t>
+          <t>39747</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65162</t>
+          <t>65055</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54619</t>
+          <t>54837</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84129</t>
+          <t>85524</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197961</t>
+          <t>198068</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223159</t>
+          <t>223376</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246835</t>
+          <t>246351</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262711</t>
+          <t>262861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>452109</t>
+          <t>450714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481619</t>
+          <t>481401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111469</t>
+          <t>110276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152842</t>
+          <t>154025</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>70005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105026</t>
+          <t>106735</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>193381</t>
+          <t>192515</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248705</t>
+          <t>252185</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>502644</t>
+          <t>501461</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>544017</t>
+          <t>545210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>584313</t>
+          <t>582604</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>619621</t>
+          <t>619334</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1096120</t>
+          <t>1092640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1151444</t>
+          <t>1152310</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119377</t>
+          <t>119065</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168070</t>
+          <t>163916</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71270</t>
+          <t>70570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109203</t>
+          <t>107494</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>200174</t>
+          <t>200081</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>257220</t>
+          <t>258074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>610513</t>
+          <t>614667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>659206</t>
+          <t>659518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>716964</t>
+          <t>718673</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>754897</t>
+          <t>755597</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1347530</t>
+          <t>1346676</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1404576</t>
+          <t>1404669</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>657993</t>
+          <t>652164</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>752729</t>
+          <t>749469</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>351550</t>
+          <t>350920</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428908</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1025856</t>
+          <t>1030338</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1154919</t>
+          <t>1155140</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2639685</t>
+          <t>2642945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2734421</t>
+          <t>2740250</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3111801</t>
+          <t>3110195</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3187553</t>
+          <t>3188183</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5776598</t>
+          <t>5776377</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5905661</t>
+          <t>5901179</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -4049,32 +4049,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35596</t>
+          <t>38854</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60566</t>
+          <t>64073</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47470</t>
+          <t>50727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73603</t>
+          <t>77201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>263894</t>
+          <t>268484</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250877</t>
+          <t>254772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275847</t>
+          <t>279991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>277547</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271413</t>
+          <t>298205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281730</t>
+          <t>307613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>541440</t>
+          <t>572109</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>527474</t>
+          <t>557705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553607</t>
+          <t>584179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>111331</t>
+          <t>119511</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91072</t>
+          <t>98856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135099</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>54402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79017</t>
+          <t>80927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>176781</t>
+          <t>186254</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154456</t>
+          <t>163914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206532</t>
+          <t>213345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>407059</t>
+          <t>411136</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383291</t>
+          <t>388197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>427318</t>
+          <t>431791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>449520</t>
+          <t>479751</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>435952</t>
+          <t>465567</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462430</t>
+          <t>492092</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>856578</t>
+          <t>890887</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>826827</t>
+          <t>863796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>878903</t>
+          <t>913227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54830</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82179</t>
+          <t>81129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62009</t>
+          <t>62094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>118242</t>
+          <t>117324</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>102681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136768</t>
+          <t>134605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>247303</t>
+          <t>248305</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233871</t>
+          <t>234864</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>261220</t>
+          <t>261602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>299632</t>
+          <t>306745</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>287119</t>
+          <t>294287</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309337</t>
+          <t>316833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>546936</t>
+          <t>555051</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>528410</t>
+          <t>537770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>563303</t>
+          <t>569694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78211</t>
+          <t>88120</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>127991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34930</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77721</t>
+          <t>77559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>152663</t>
+          <t>172525</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111080</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>196745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>218083</t>
+          <t>265714</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197499</t>
+          <t>245154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234346</t>
+          <t>285025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>417528</t>
+          <t>356867</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>397997</t>
+          <t>344402</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>440788</t>
+          <t>369127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>635611</t>
+          <t>622582</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>606073</t>
+          <t>598362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>677194</t>
+          <t>644908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,32 +5421,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,32 +5456,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>163930</t>
+          <t>189968</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157868</t>
+          <t>183526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169058</t>
+          <t>195011</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>200330</t>
+          <t>218383</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195288</t>
+          <t>212816</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203486</t>
+          <t>221862</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>364260</t>
+          <t>408351</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357095</t>
+          <t>399365</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>370580</t>
+          <t>414448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>35601</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56427</t>
+          <t>55009</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46876</t>
+          <t>45564</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70213</t>
+          <t>68743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>224254</t>
+          <t>226171</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213209</t>
+          <t>215698</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233395</t>
+          <t>235106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>246032</t>
+          <t>252250</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239934</t>
+          <t>245654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250071</t>
+          <t>256592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>470286</t>
+          <t>478421</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>456479</t>
+          <t>465714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>479816</t>
+          <t>488893</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>122914</t>
+          <t>143540</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104130</t>
+          <t>121687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141819</t>
+          <t>166507</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>95418</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39596</t>
+          <t>90182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131943</t>
+          <t>126155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>218332</t>
+          <t>251601</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>138258</t>
+          <t>225896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262808</t>
+          <t>281081</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>500171</t>
+          <t>573887</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>481266</t>
+          <t>550920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>518955</t>
+          <t>595740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>749941</t>
+          <t>660125</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>713416</t>
+          <t>642030</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>805763</t>
+          <t>678003</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1250112</t>
+          <t>1234011</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1205636</t>
+          <t>1204531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1330186</t>
+          <t>1259716</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>84,79%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623085</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623085</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623085</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>845359</t>
+          <t>768185</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845359</t>
+          <t>768185</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>845359</t>
+          <t>768185</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1468444</t>
+          <t>1485612</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1468444</t>
+          <t>1485612</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1468444</t>
+          <t>1485612</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>347229</t>
+          <t>114644</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130443</t>
+          <t>96337</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>654262</t>
+          <t>133281</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,32 +6485,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>56759</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>385275</t>
+          <t>158885</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158441</t>
+          <t>136197</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>853817</t>
+          <t>180420</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>580488</t>
+          <t>682286</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>273455</t>
+          <t>663649</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>797274</t>
+          <t>700593</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,32 +6598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>679684</t>
+          <t>787090</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>669311</t>
+          <t>774572</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>688626</t>
+          <t>796805</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1260174</t>
+          <t>1469377</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>791632</t>
+          <t>1447842</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1487008</t>
+          <t>1492065</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1645449</t>
+          <t>1628262</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1645449</t>
+          <t>1628262</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1645449</t>
+          <t>1628262</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>852438</t>
+          <t>663408</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>641386</t>
+          <t>618433</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1477012</t>
+          <t>708368</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>338037</t>
+          <t>366543</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>337336</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>377059</t>
+          <t>398317</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1190474</t>
+          <t>1029951</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>950224</t>
+          <t>976529</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1829952</t>
+          <t>1084078</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2605182</t>
+          <t>2865953</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1980608</t>
+          <t>2820993</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2816234</t>
+          <t>2910928</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3320214</t>
+          <t>3364837</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3281192</t>
+          <t>3333063</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3382553</t>
+          <t>3394044</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5925397</t>
+          <t>6230789</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5285919</t>
+          <t>6176662</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6165647</t>
+          <t>6284211</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
